--- a/02_加值成品/八下/八下4-1_三種難度測驗卷.xlsx
+++ b/02_加值成品/八下/八下4-1_三種難度測驗卷.xlsx
@@ -490,19 +490,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國二下學期 八下4-1 反應速率　測驗　★☆☆ 基礎（記憶・理解）</t>
+          <t>國二下學期 八下4-1 反應速率　測驗　★☆☆ 基礎（記憶・理解）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -519,16 +523,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -537,18 +561,38 @@
           <t>反應速率表示反應的？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>增加量</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>反應速率</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>快慢</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>碰撞</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>速度</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -557,18 +601,38 @@
           <t>反應靠粒子什麼發生？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>降低反應速率</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>快慢</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>不能</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>碰撞</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>接觸</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -577,18 +641,38 @@
           <t>能引發反應的碰撞稱？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>有效碰撞</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
+          <t>快</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>增加量</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>不是</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
           <t>成功</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -597,18 +681,38 @@
           <t>反應需達到什麼能量？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>不是</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>減少量</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>越快</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>活化能</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>能障</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -617,18 +721,38 @@
           <t>速率可由生成物什麼衡量？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>不是</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>快</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>增加量</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>慢</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>單位時間</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -637,18 +761,38 @@
           <t>每次碰撞都反應嗎？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>快慢</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>慢</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>有效碰撞</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>不是</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>需有效</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -657,18 +801,38 @@
           <t>冷藏食物是為了？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>不能</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>降低反應速率</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>快</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>越快</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>保鮮</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -677,18 +841,38 @@
           <t>鐵生鏽是快還慢反應？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>慢</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
+          <t>快慢</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>不是</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>碰撞</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
           <t>緩慢</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -697,18 +881,38 @@
           <t>反應進行的快慢稱？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>活化能</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>降低反應速率</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>反應速率</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>快</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>速率</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -717,12 +921,32 @@
           <t>反應需要粒子有效的什麼？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>慢</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>不能</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>活化能</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>碰撞</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>碰撞</t>
         </is>
@@ -730,7 +954,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -742,19 +966,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國二下學期 八下4-1 反應速率　測驗　★★☆ 進階（應用・分析）</t>
+          <t>國二下學期 八下4-1 反應速率　測驗　★★☆ 進階（應用・分析）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -771,16 +999,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -789,18 +1037,38 @@
           <t>反應速率可測哪些變化？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>氣體體積/質量/顏色</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
+          <t>量單位時間產生氫氣體積</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>活化能與碰撞頻率不同</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>除溫度外其他條件相同</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
           <t>觀測</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -809,18 +1077,38 @@
           <t>有效碰撞需哪兩條件？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>足夠能量與正確方向</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
+          <t>低溫粒子動能小、有效碰撞少</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>活化能與碰撞頻率不同</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>氣體體積/質量/顏色</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
           <t>雙條件</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -829,18 +1117,38 @@
           <t>鞭炮爆炸是快還慢反應？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>快慢</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>有效碰撞</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>降低反應速率</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>快</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>瞬間</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -849,18 +1157,38 @@
           <t>碰撞越頻繁有效反應？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>快慢</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>減少量</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>不能</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>越快</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>速率增</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -869,18 +1197,38 @@
           <t>測產生氣體反應速率可量？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>活化能與碰撞頻率不同</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>量單位時間產生氫氣體積</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>氣體體積隨時間</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>除溫度外其他條件相同</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>方法</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -889,18 +1237,38 @@
           <t>反應物減少速率可代表？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>降低反應速率</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>增加量</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>反應速率</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>減少量</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>衡量</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -909,18 +1277,38 @@
           <t>活化能越高反應越？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>降低反應速率</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>快慢</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>增加量</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>慢</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>難達</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -929,18 +1317,38 @@
           <t>顆粒間沒接觸能反應嗎？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>活化能</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>降低反應速率</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>不能</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>不是</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>需碰撞</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -949,18 +1357,38 @@
           <t>活化能是引發反應所需的？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>最低能量</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
+          <t>降低反應速率</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>有效碰撞</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>減少量</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
           <t>能障</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -969,12 +1397,32 @@
           <t>速率可用單位時間反應物的什麼衡量？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>反應速率</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
         <is>
           <t>減少量</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>有效碰撞</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>降低反應速率</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>衡量</t>
         </is>
@@ -982,7 +1430,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -994,19 +1442,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國二下學期 八下4-1 反應速率　測驗　★★★ 挑戰（評鑑・創造）</t>
+          <t>國二下學期 八下4-1 反應速率　測驗　★★★ 挑戰（評鑑・創造）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -1023,16 +1475,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -1041,18 +1513,38 @@
           <t>如何設計實驗測鎂與酸反應速率？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>量單位時間產生氫氣體積</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
+          <t>氣體體積隨時間</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>需同時滿足能量與方向</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>氣體體積/質量/顏色</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
           <t>實驗</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -1061,18 +1553,38 @@
           <t>為何不是每次碰撞都反應？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>需同時滿足能量與方向</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
+          <t>低溫粒子動能小、有效碰撞少</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>氣體體積/質量/顏色</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>活化能與碰撞頻率不同</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
           <t>碰撞學說</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -1081,18 +1593,38 @@
           <t>用碰撞學說解釋為何冷藏保鮮？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>速率=變化量/時間</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>活化能與碰撞頻率不同</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>低溫粒子動能小、有效碰撞少</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>需同時滿足能量與方向</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>應用</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -1101,18 +1633,38 @@
           <t>反應初期速率通常較快因為？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>反應物濃度高碰撞多</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
+          <t>除溫度外其他條件相同</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>足夠能量與正確方向</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>活化能與碰撞頻率不同</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
           <t>濃度</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -1121,18 +1673,38 @@
           <t>比較爆炸與生鏽的速率差異原因？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>活化能與碰撞頻率不同</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
+          <t>反應物濃度高碰撞多</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>氣體體積/質量/顏色</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>除溫度外其他條件相同</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
           <t>分析</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -1141,18 +1713,38 @@
           <t>測量反應速率為何要記時間？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>活化能與碰撞頻率不同</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>低溫粒子動能小、有效碰撞少</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>引發反應所需最低能量</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>速率=變化量/時間</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>定義</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -1161,18 +1753,38 @@
           <t>反應到後期速率變慢因為？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>反應物變少碰撞減少</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
+          <t>需同時滿足能量與方向</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>反應物濃度高碰撞多</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>量單位時間產生氫氣體積</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
           <t>耗盡</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -1181,18 +1793,38 @@
           <t>活化能的意義是？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>速率=變化量/時間</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>活化能與碰撞頻率不同</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>氣體體積/質量/顏色</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>引發反應所需最低能量</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>門檻</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -1201,18 +1833,38 @@
           <t>比較兩溫度下反應快慢要控制什麼？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>除溫度外其他條件相同</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
+          <t>反應物濃度高碰撞多</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>氣體體積隨時間</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>氣體體積/質量/顏色</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
           <t>控制變因</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -1221,12 +1873,32 @@
           <t>反應後期速率變慢的原因？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>反應物濃度高碰撞多</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
         <is>
           <t>反應物減少碰撞變少</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>氣體體積隨時間</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>量單位時間產生氫氣體積</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>耗盡</t>
         </is>
@@ -1234,7 +1906,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/02_加值成品/八下/八下4-1_三種難度測驗卷.xlsx
+++ b/02_加值成品/八下/八下4-1_三種難度測驗卷.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>速度</t>
+          <t>速度：反應速率就是用來描述一個化學反應進行得有多快或多慢的量</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>接觸</t>
+          <t>接觸：反應物中的粒子必須互相撞在一起接觸，反應才有可能發生</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>成功</t>
+          <t>成功：不是隨便撞一下就會反應，只有能量和方向都對的碰撞才能成功引發反應</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>能障</t>
+          <t>能障：粒子要越過一個能量門檻才能發生反應，這個門檻就叫做活化能</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>單位時間</t>
+          <t>單位時間：觀察每過一段固定時間，生成物增加了多少量，就能算出反應速率</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>需有效</t>
+          <t>需有效：粒子雖然常常互相碰撞，但只有滿足條件的有效碰撞才會真正發生反應</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>保鮮</t>
+          <t>保鮮：低溫會讓造成食物腐壞的反應變慢，所以冷藏能延長食物保存的時間</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>緩慢</t>
+          <t>緩慢：鐵和氧氣結合生鏽需要很長的時間才會明顯看出變化，屬於進行得很慢的反應</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>速率</t>
+          <t>速率：化學反應進行的快慢程度，稱為反應速率</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>碰撞</t>
+          <t>碰撞：化學反應要發生，反應物的粒子之間必須先產生有效的碰撞才行</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>觀測</t>
+          <t>觀測：可以透過測量反應中產生氣體的體積、質量的減少，或顏色隨時間的改變來判斷速率</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>雙條件</t>
+          <t>雙條件：粒子碰撞時不但要帶有足夠的能量越過活化能，撞擊的角度和方向也要恰當才行</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>瞬間</t>
+          <t>瞬間：鞭炮爆炸的反應在極短的時間內就完成，是速率非常快的反應例子</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>速率增</t>
+          <t>速率增：粒子彼此碰撞的次數越多，其中能成功引發反應的有效碰撞也會跟著增加，速率就變快</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>方法</t>
+          <t>方法：把產生的氣體收集起來，記錄不同時間點的體積變化，就能算出反應進行的快慢</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>衡量</t>
+          <t>衡量：反應物被消耗得越快，代表這個反應進行的速率也越快，兩者可以互相對應</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>難達</t>
+          <t>難達：活化能像一道很高的門檻，門檻越高，粒子就越難達到，反應也就進行得越慢</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>需碰撞</t>
+          <t>需碰撞：反應物的粒子如果完全沒有互相接觸碰撞，就不可能發生化學反應</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>能障</t>
+          <t>能障：要讓反應發生，反應物粒子碰撞時至少需要具備的最低能量稱為活化能，是反應必須跨越的能量門檻</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>衡量</t>
+          <t>衡量：反應速率可以用單位時間內反應物濃度或質量減少的量來衡量，減少得越快代表反應速率越快</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>實驗</t>
+          <t>實驗：把鎂帶加入酸中，用集氣裝置收集反應產生的氫氣，記錄不同時間收集到的氣體體積</t>
         </is>
       </c>
     </row>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>碰撞學說</t>
+          <t>碰撞學說：粒子碰撞時如果能量不夠或撞擊角度不對，就無法讓原本的鍵結拆開重組，反應不會發生</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>應用</t>
+          <t>應用：溫度低時粒子移動速度慢、能量也小，能成功引發反應的有效碰撞變少，所以食物變質得比較慢</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>濃度</t>
+          <t>濃度：反應剛開始時反應物的量還很多，粒子密集容易碰撞，所以一開始的反應速率通常比較快</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>分析</t>
+          <t>分析：爆炸的活化能低、碰撞又劇烈頻繁，生鏽的活化能相對高且碰撞不頻繁，所以兩者速率差異很大</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>定義</t>
+          <t>定義：反應速率的定義就是變化的量除以所花費的時間，沒有時間這個數字就沒辦法算出速率</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>耗盡</t>
+          <t>耗盡：隨著反應進行，可以互相碰撞的反應物粒子越來越少，有效碰撞的機會也跟著減少，速率變慢</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>門檻</t>
+          <t>門檻：活化能代表粒子要發生反應之前，至少必須具備的最低能量標準</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>控制變因</t>
+          <t>控制變因：要單獨比較溫度對反應速率的影響，必須讓濃度、接觸面積等其他條件保持相同，只改變溫度這個變因，這樣的比較才公平準確</t>
         </is>
       </c>
     </row>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>耗盡</t>
+          <t>耗盡：反應進行到後期，反應物的濃度或數量逐漸減少，粒子間有效碰撞的機會也跟著變少，所以反應速率會逐漸變慢</t>
         </is>
       </c>
     </row>

--- a/02_加值成品/八下/八下4-1_三種難度測驗卷.xlsx
+++ b/02_加值成品/八下/八下4-1_三種難度測驗卷.xlsx
@@ -563,22 +563,22 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
+          <t>不是</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>有效碰撞</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>快慢</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
           <t>增加量</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>反應速率</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>快慢</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>碰撞</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
@@ -603,17 +603,17 @@
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
+          <t>慢</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
           <t>降低反應速率</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
-        <is>
-          <t>快慢</t>
-        </is>
-      </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>不能</t>
+          <t>快</t>
         </is>
       </c>
       <c r="F4" s="7" t="inlineStr">
@@ -648,17 +648,17 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>快</t>
+          <t>增加量</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>增加量</t>
+          <t>快慢</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>不是</t>
+          <t>降低反應速率</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
@@ -803,7 +803,7 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>不能</t>
+          <t>有效碰撞</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -813,12 +813,12 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>快</t>
+          <t>最低能量</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>越快</t>
+          <t>不是</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
@@ -848,17 +848,17 @@
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>快慢</t>
+          <t>降低反應速率</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
+          <t>反應速率</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
           <t>不是</t>
-        </is>
-      </c>
-      <c r="F10" s="7" t="inlineStr">
-        <is>
-          <t>碰撞</t>
         </is>
       </c>
       <c r="G10" s="8" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>活化能</t>
+          <t>越快</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>降低反應速率</t>
+          <t>不是</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>快</t>
+          <t>慢</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
@@ -923,17 +923,17 @@
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>慢</t>
+          <t>不是</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>不能</t>
+          <t>越快</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>活化能</t>
+          <t>快慢</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
@@ -1119,17 +1119,17 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>快慢</t>
+          <t>活化能</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>有效碰撞</t>
+          <t>最低能量</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>降低反應速率</t>
+          <t>碰撞</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -1159,17 +1159,17 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
+          <t>活化能</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>碰撞</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
           <t>快慢</t>
-        </is>
-      </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>減少量</t>
-        </is>
-      </c>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>不能</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>降低反應速率</t>
+          <t>不是</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>增加量</t>
+          <t>不能</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
@@ -1254,7 +1254,7 @@
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>減少量</t>
+          <t>活化能</t>
         </is>
       </c>
       <c r="G8" s="8" t="inlineStr">
@@ -1279,17 +1279,17 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>降低反應速率</t>
+          <t>有效碰撞</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>快慢</t>
+          <t>增加量</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>增加量</t>
+          <t>碰撞</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
